--- a/salidas/empresas/BX.xlsx
+++ b/salidas/empresas/BX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B2" t="n">
-        <v>10.64566040039062</v>
+        <v>10.64566326141357</v>
       </c>
       <c r="C2" t="n">
         <v>28.72423934936523</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B3" t="n">
-        <v>8.732565879821777</v>
+        <v>8.73256778717041</v>
       </c>
       <c r="C3" t="n">
         <v>23.56231689453125</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B4" t="n">
-        <v>8.412508964538574</v>
+        <v>8.412506103515625</v>
       </c>
       <c r="C4" t="n">
         <v>22.6987247467041</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B5" t="n">
-        <v>9.121733665466309</v>
+        <v>9.121734619140625</v>
       </c>
       <c r="C5" t="n">
         <v>24.61236572265625</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B6" t="n">
-        <v>9.249032974243164</v>
+        <v>9.249029159545898</v>
       </c>
       <c r="C6" t="n">
         <v>24.95583915710449</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B8" t="n">
-        <v>8.166362762451172</v>
+        <v>8.16635799407959</v>
       </c>
       <c r="C8" t="n">
         <v>21.71736907958984</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B9" t="n">
-        <v>6.771471500396729</v>
+        <v>6.77147102355957</v>
       </c>
       <c r="C9" t="n">
         <v>18.00785064697266</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B10" t="n">
-        <v>6.088789463043213</v>
+        <v>6.088790893554688</v>
       </c>
       <c r="C10" t="n">
         <v>16.19234466552734</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B11" t="n">
-        <v>5.970844268798828</v>
+        <v>5.97084379196167</v>
       </c>
       <c r="C11" t="n">
         <v>15.58390617370605</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B12" t="n">
-        <v>7.019874095916748</v>
+        <v>7.019876003265381</v>
       </c>
       <c r="C12" t="n">
         <v>18.32188415527344</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B13" t="n">
-        <v>7.438686847686768</v>
+        <v>7.438689708709717</v>
       </c>
       <c r="C13" t="n">
         <v>19.10696792602539</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B14" t="n">
-        <v>6.957293510437012</v>
+        <v>6.957295417785645</v>
       </c>
       <c r="C14" t="n">
         <v>17.87046051025391</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B15" t="n">
-        <v>7.094834804534912</v>
+        <v>7.094835758209229</v>
       </c>
       <c r="C15" t="n">
         <v>18.2237491607666</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B16" t="n">
-        <v>6.952334403991699</v>
+        <v>6.952335357666016</v>
       </c>
       <c r="C16" t="n">
         <v>17.5466136932373</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B17" t="n">
-        <v>5.96469783782959</v>
+        <v>5.964700222015381</v>
       </c>
       <c r="C17" t="n">
         <v>15.05397415161133</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B18" t="n">
-        <v>3.553934812545776</v>
+        <v>3.553936004638672</v>
       </c>
       <c r="C18" t="n">
         <v>8.969577789306641</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B19" t="n">
-        <v>2.553218126296997</v>
+        <v>2.553218603134155</v>
       </c>
       <c r="C19" t="n">
         <v>6.143278121948242</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B20" t="n">
-        <v>2.663341522216797</v>
+        <v>2.663341999053955</v>
       </c>
       <c r="C20" t="n">
         <v>6.408243179321289</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B21" t="n">
-        <v>1.839459419250488</v>
+        <v>1.839459776878357</v>
       </c>
       <c r="C21" t="n">
         <v>4.425908088684082</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B22" t="n">
-        <v>1.98629105091095</v>
+        <v>1.986289620399475</v>
       </c>
       <c r="C22" t="n">
         <v>4.779194831848145</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B23" t="n">
-        <v>2.957001447677612</v>
+        <v>2.957001924514771</v>
       </c>
       <c r="C23" t="n">
         <v>7.114818096160889</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B24" t="n">
-        <v>3.992972612380981</v>
+        <v>3.992974042892456</v>
       </c>
       <c r="C24" t="n">
         <v>9.607458114624023</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B26" t="n">
-        <v>4.414533138275146</v>
+        <v>4.414534568786621</v>
       </c>
       <c r="C26" t="n">
         <v>10.34347438812256</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B27" t="n">
-        <v>4.71609354019165</v>
+        <v>4.716098308563232</v>
       </c>
       <c r="C27" t="n">
         <v>11.050048828125</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B28" t="n">
-        <v>5.525333404541016</v>
+        <v>5.52533483505249</v>
       </c>
       <c r="C28" t="n">
         <v>12.64965724945068</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B29" t="n">
-        <v>6.086867332458496</v>
+        <v>6.086868762969971</v>
       </c>
       <c r="C29" t="n">
         <v>13.93523120880127</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B30" t="n">
-        <v>5.752518177032471</v>
+        <v>5.752519607543945</v>
       </c>
       <c r="C30" t="n">
         <v>13.16977405548096</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B31" t="n">
-        <v>6.062177658081055</v>
+        <v>6.062180042266846</v>
       </c>
       <c r="C31" t="n">
         <v>13.58194255828857</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B32" t="n">
-        <v>5.74680757522583</v>
+        <v>5.746806621551514</v>
       </c>
       <c r="C32" t="n">
         <v>12.87536811828613</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B33" t="n">
-        <v>5.31316614151001</v>
+        <v>5.313168048858643</v>
       </c>
       <c r="C33" t="n">
         <v>11.90382671356201</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B34" t="n">
-        <v>6.123503684997559</v>
+        <v>6.123501777648926</v>
       </c>
       <c r="C34" t="n">
         <v>13.71933269500732</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B35" t="n">
-        <v>6.258788585662842</v>
+        <v>6.258786678314209</v>
       </c>
       <c r="C35" t="n">
         <v>13.73896026611328</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B36" t="n">
-        <v>6.249847888946533</v>
+        <v>6.249846935272217</v>
       </c>
       <c r="C36" t="n">
         <v>13.71933269500732</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B37" t="n">
-        <v>4.797998905181885</v>
+        <v>4.798001289367676</v>
       </c>
       <c r="C37" t="n">
         <v>10.45142269134521</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B38" t="n">
-        <v>4.306939601898193</v>
+        <v>4.306937694549561</v>
       </c>
       <c r="C38" t="n">
         <v>9.381747245788574</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B39" t="n">
-        <v>5.023258209228516</v>
+        <v>5.023258686065674</v>
       </c>
       <c r="C39" t="n">
         <v>10.94209957122803</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B40" t="n">
-        <v>4.587453365325928</v>
+        <v>4.587451934814453</v>
       </c>
       <c r="C40" t="n">
         <v>9.901865005493164</v>
@@ -1229,11 +1241,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B41" t="n">
-        <v>5.769551753997803</v>
+        <v>5.769554138183594</v>
       </c>
       <c r="C41" t="n">
         <v>12.4533863067627</v>
@@ -1254,11 +1266,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B42" t="n">
-        <v>6.128730297088623</v>
+        <v>6.12872838973999</v>
       </c>
       <c r="C42" t="n">
         <v>13.22865581512451</v>
@@ -1279,11 +1291,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B43" t="n">
-        <v>5.861734867095947</v>
+        <v>5.861732006072998</v>
       </c>
       <c r="C43" t="n">
         <v>12.56133460998535</v>
@@ -1304,11 +1316,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B44" t="n">
-        <v>6.479965209960938</v>
+        <v>6.479964733123779</v>
       </c>
       <c r="C44" t="n">
         <v>13.88616275787354</v>
@@ -1329,11 +1341,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B45" t="n">
-        <v>7.2035231590271</v>
+        <v>7.203522682189941</v>
       </c>
       <c r="C45" t="n">
         <v>15.43670272827148</v>
@@ -1354,11 +1366,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B46" t="n">
-        <v>8.15147590637207</v>
+        <v>8.151474952697754</v>
       </c>
       <c r="C46" t="n">
         <v>17.46810531616211</v>
@@ -1379,11 +1391,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B47" t="n">
-        <v>8.340091705322266</v>
+        <v>8.340094566345215</v>
       </c>
       <c r="C47" t="n">
         <v>17.5466136932373</v>
@@ -1404,11 +1416,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B48" t="n">
-        <v>8.834529876708984</v>
+        <v>8.834528923034668</v>
       </c>
       <c r="C48" t="n">
         <v>18.58684921264648</v>
@@ -1429,11 +1441,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B49" t="n">
-        <v>8.133001327514648</v>
+        <v>8.132999420166016</v>
       </c>
       <c r="C49" t="n">
         <v>16.91854858398438</v>
@@ -1454,11 +1466,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B50" t="n">
-        <v>7.812206268310547</v>
+        <v>7.812207221984863</v>
       </c>
       <c r="C50" t="n">
         <v>16.2512264251709</v>
@@ -1479,11 +1491,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B51" t="n">
-        <v>7.835795402526855</v>
+        <v>7.835797786712646</v>
       </c>
       <c r="C51" t="n">
         <v>16.30029487609863</v>
@@ -1504,7 +1516,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B52" t="n">
@@ -1529,11 +1541,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B53" t="n">
-        <v>5.697835445404053</v>
+        <v>5.697836399078369</v>
       </c>
       <c r="C53" t="n">
         <v>11.75662422180176</v>
@@ -1554,11 +1566,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B54" t="n">
-        <v>6.996253490447998</v>
+        <v>6.996255874633789</v>
       </c>
       <c r="C54" t="n">
         <v>14.4357213973999</v>
@@ -1579,11 +1591,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B55" t="n">
-        <v>6.579293251037598</v>
+        <v>6.579293727874756</v>
       </c>
       <c r="C55" t="n">
         <v>13.47399425506592</v>
@@ -1604,11 +1616,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B56" t="n">
-        <v>6.713462352752686</v>
+        <v>6.713461875915527</v>
       </c>
       <c r="C56" t="n">
         <v>13.74877262115479</v>
@@ -1629,11 +1641,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B57" t="n">
-        <v>7.576010227203369</v>
+        <v>7.576007843017578</v>
       </c>
       <c r="C57" t="n">
         <v>15.51521110534668</v>
@@ -1654,11 +1666,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B58" t="n">
-        <v>7.48496150970459</v>
+        <v>7.484961986541748</v>
       </c>
       <c r="C58" t="n">
         <v>15.32875442504883</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B59" t="n">
-        <v>7.750626564025879</v>
+        <v>7.750629901885986</v>
       </c>
       <c r="C59" t="n">
         <v>15.64278697967529</v>
@@ -1708,11 +1720,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B60" t="n">
-        <v>6.593386650085449</v>
+        <v>6.593387603759766</v>
       </c>
       <c r="C60" t="n">
         <v>13.30716419219971</v>
@@ -1735,11 +1747,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B61" t="n">
-        <v>5.900766849517822</v>
+        <v>5.900765419006348</v>
       </c>
       <c r="C61" t="n">
         <v>11.815505027771</v>
@@ -1762,11 +1774,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B62" t="n">
-        <v>6.405566215515137</v>
+        <v>6.405564308166504</v>
       </c>
       <c r="C62" t="n">
         <v>12.8262996673584</v>
@@ -1789,7 +1801,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B63" t="n">
@@ -1816,11 +1828,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B64" t="n">
-        <v>6.659879207611084</v>
+        <v>6.659877300262451</v>
       </c>
       <c r="C64" t="n">
         <v>13.23846912384033</v>
@@ -1843,11 +1855,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B65" t="n">
-        <v>7.049890041351318</v>
+        <v>7.049894332885742</v>
       </c>
       <c r="C65" t="n">
         <v>14.01373863220215</v>
@@ -1870,11 +1882,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B66" t="n">
-        <v>7.583076477050781</v>
+        <v>7.583080291748047</v>
       </c>
       <c r="C66" t="n">
         <v>15.07360172271729</v>
@@ -1897,11 +1909,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B67" t="n">
-        <v>7.302668571472168</v>
+        <v>7.302669525146484</v>
       </c>
       <c r="C67" t="n">
         <v>14.41609382629395</v>
@@ -1926,11 +1938,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B68" t="n">
-        <v>7.750072479248047</v>
+        <v>7.750074863433838</v>
       </c>
       <c r="C68" t="n">
         <v>15.29931259155273</v>
@@ -1955,11 +1967,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B69" t="n">
-        <v>9.196688652038574</v>
+        <v>9.196682929992676</v>
       </c>
       <c r="C69" t="n">
         <v>18.15505409240723</v>
@@ -1984,7 +1996,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B70" t="n">
@@ -2013,11 +2025,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B71" t="n">
-        <v>10.05966758728027</v>
+        <v>10.05966663360596</v>
       </c>
       <c r="C71" t="n">
         <v>19.41118621826172</v>
@@ -2042,11 +2054,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B72" t="n">
-        <v>10.60587596893311</v>
+        <v>10.60587692260742</v>
       </c>
       <c r="C72" t="n">
         <v>20.16683006286621</v>
@@ -2071,11 +2083,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B73" t="n">
-        <v>11.29744815826416</v>
+        <v>11.29745101928711</v>
       </c>
       <c r="C73" t="n">
         <v>21.48184585571289</v>
@@ -2100,7 +2112,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B74" t="n">
@@ -2129,11 +2141,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B75" t="n">
-        <v>11.75188541412354</v>
+        <v>11.75188827514648</v>
       </c>
       <c r="C75" t="n">
         <v>22.12953948974609</v>
@@ -2158,11 +2170,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B76" t="n">
-        <v>11.38187217712402</v>
+        <v>11.38187026977539</v>
       </c>
       <c r="C76" t="n">
         <v>21.43277740478516</v>
@@ -2187,11 +2199,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B77" t="n">
-        <v>12.9713773727417</v>
+        <v>12.97137260437012</v>
       </c>
       <c r="C77" t="n">
         <v>24.42590713500977</v>
@@ -2216,11 +2228,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B78" t="n">
-        <v>13.81081390380859</v>
+        <v>13.81081581115723</v>
       </c>
       <c r="C78" t="n">
         <v>25.78998947143555</v>
@@ -2245,11 +2257,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B79" t="n">
-        <v>15.01952648162842</v>
+        <v>15.01951885223389</v>
       </c>
       <c r="C79" t="n">
         <v>28.04710578918457</v>
@@ -2274,7 +2286,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B80" t="n">
@@ -2303,11 +2315,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B81" t="n">
-        <v>17.21096420288086</v>
+        <v>17.21096611022949</v>
       </c>
       <c r="C81" t="n">
         <v>32.13935089111328</v>
@@ -2332,11 +2344,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B82" t="n">
-        <v>17.8523998260498</v>
+        <v>17.85240364074707</v>
       </c>
       <c r="C82" t="n">
         <v>32.72816467285156</v>
@@ -2361,11 +2373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B83" t="n">
-        <v>17.79887580871582</v>
+        <v>17.79887771606445</v>
       </c>
       <c r="C83" t="n">
         <v>32.63002777099609</v>
@@ -2390,11 +2402,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B84" t="n">
-        <v>15.97957229614258</v>
+        <v>15.97957515716553</v>
       </c>
       <c r="C84" t="n">
         <v>28.97939109802246</v>
@@ -2419,7 +2431,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B85" t="n">
@@ -2448,11 +2460,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B86" t="n">
-        <v>18.09539413452148</v>
+        <v>18.09539794921875</v>
       </c>
       <c r="C86" t="n">
         <v>32.81648635864258</v>
@@ -2477,11 +2489,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B87" t="n">
-        <v>17.95834541320801</v>
+        <v>17.95834922790527</v>
       </c>
       <c r="C87" t="n">
         <v>32.07065963745117</v>
@@ -2506,11 +2518,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B88" t="n">
-        <v>18.42544364929199</v>
+        <v>18.42543792724609</v>
       </c>
       <c r="C88" t="n">
         <v>32.90480804443359</v>
@@ -2535,11 +2547,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B89" t="n">
-        <v>17.29892158508301</v>
+        <v>17.29892539978027</v>
       </c>
       <c r="C89" t="n">
         <v>30.89303207397461</v>
@@ -2564,11 +2576,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B90" t="n">
-        <v>16.79129791259766</v>
+        <v>16.79129600524902</v>
       </c>
       <c r="C90" t="n">
         <v>29.55839157104492</v>
@@ -2593,7 +2605,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B91" t="n">
@@ -2622,11 +2634,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B92" t="n">
-        <v>18.85954666137695</v>
+        <v>18.85954284667969</v>
       </c>
       <c r="C92" t="n">
         <v>33.19921493530273</v>
@@ -2651,11 +2663,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B93" t="n">
-        <v>20.81629753112793</v>
+        <v>20.8163013458252</v>
       </c>
       <c r="C93" t="n">
         <v>36.64376831054688</v>
@@ -2680,11 +2692,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B94" t="n">
-        <v>21.3304500579834</v>
+        <v>21.33044624328613</v>
       </c>
       <c r="C94" t="n">
         <v>36.76153182983398</v>
@@ -2709,11 +2721,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B95" t="n">
-        <v>22.14471435546875</v>
+        <v>22.14472007751465</v>
       </c>
       <c r="C95" t="n">
         <v>38.16486740112305</v>
@@ -2738,11 +2750,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B96" t="n">
-        <v>23.83131217956543</v>
+        <v>23.83131980895996</v>
       </c>
       <c r="C96" t="n">
         <v>40.19626998901367</v>
@@ -2767,11 +2779,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B97" t="n">
-        <v>25.48367691040039</v>
+        <v>25.48368835449219</v>
       </c>
       <c r="C97" t="n">
         <v>42.98331832885742</v>
@@ -2796,11 +2808,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B98" t="n">
-        <v>23.77894592285156</v>
+        <v>23.77895164489746</v>
       </c>
       <c r="C98" t="n">
         <v>40.10794830322266</v>
@@ -2825,11 +2837,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B99" t="n">
-        <v>23.25099754333496</v>
+        <v>23.25100326538086</v>
       </c>
       <c r="C99" t="n">
         <v>38.51815414428711</v>
@@ -2854,11 +2866,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B100" t="n">
-        <v>20.28908348083496</v>
+        <v>20.28908538818359</v>
       </c>
       <c r="C100" t="n">
         <v>33.61138534545898</v>
@@ -2883,11 +2895,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B101" t="n">
-        <v>18.76074409484863</v>
+        <v>18.7607421875</v>
       </c>
       <c r="C101" t="n">
         <v>31.07949066162109</v>
@@ -2912,11 +2924,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B102" t="n">
-        <v>20.25141334533691</v>
+        <v>20.25140762329102</v>
       </c>
       <c r="C102" t="n">
         <v>33.06000137329102</v>
@@ -2941,11 +2953,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B103" t="n">
-        <v>19.13041687011719</v>
+        <v>19.13041496276855</v>
       </c>
       <c r="C103" t="n">
         <v>31.22999954223633</v>
@@ -2970,11 +2982,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B104" t="n">
-        <v>17.91140747070312</v>
+        <v>17.91141128540039</v>
       </c>
       <c r="C104" t="n">
         <v>29.23999977111816</v>
@@ -2999,11 +3011,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B105" t="n">
-        <v>16.09209442138672</v>
+        <v>16.09208869934082</v>
       </c>
       <c r="C105" t="n">
         <v>26.27000045776367</v>
@@ -3028,11 +3040,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B106" t="n">
-        <v>16.28357315063477</v>
+        <v>16.28357124328613</v>
       </c>
       <c r="C106" t="n">
         <v>25.96999931335449</v>
@@ -3057,11 +3069,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B107" t="n">
-        <v>17.58776664733887</v>
+        <v>17.58776473999023</v>
       </c>
       <c r="C107" t="n">
         <v>28.04999923706055</v>
@@ -3086,11 +3098,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B108" t="n">
-        <v>17.37397003173828</v>
+        <v>17.37396621704102</v>
       </c>
       <c r="C108" t="n">
         <v>27.44000053405762</v>
@@ -3115,11 +3127,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B109" t="n">
-        <v>16.58251762390137</v>
+        <v>16.58251190185547</v>
       </c>
       <c r="C109" t="n">
         <v>26.19000053405762</v>
@@ -3144,11 +3156,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B110" t="n">
-        <v>15.53779792785645</v>
+        <v>15.53779220581055</v>
       </c>
       <c r="C110" t="n">
         <v>24.54000091552734</v>
@@ -3173,7 +3185,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B111" t="n">
@@ -3202,7 +3214,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B112" t="n">
@@ -3231,7 +3243,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B113" t="n">
@@ -3260,11 +3272,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B114" t="n">
-        <v>16.05825996398926</v>
+        <v>16.05826377868652</v>
       </c>
       <c r="C114" t="n">
         <v>25.03000068664551</v>
@@ -3289,7 +3301,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B115" t="n">
@@ -3318,11 +3330,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B116" t="n">
-        <v>17.63825035095215</v>
+        <v>17.63825607299805</v>
       </c>
       <c r="C116" t="n">
         <v>27.03000068664551</v>
@@ -3347,7 +3359,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B117" t="n">
@@ -3376,11 +3388,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B118" t="n">
-        <v>19.57134246826172</v>
+        <v>19.57133674621582</v>
       </c>
       <c r="C118" t="n">
         <v>29.54000091552734</v>
@@ -3405,11 +3417,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
-        <v>19.67734909057617</v>
+        <v>19.67734718322754</v>
       </c>
       <c r="C119" t="n">
         <v>29.70000076293945</v>
@@ -3434,7 +3446,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B120" t="n">
@@ -3463,7 +3475,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B121" t="n">
@@ -3492,7 +3504,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B122" t="n">
@@ -3521,11 +3533,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B123" t="n">
-        <v>23.15868759155273</v>
+        <v>23.1586799621582</v>
       </c>
       <c r="C123" t="n">
         <v>33.45000076293945</v>
@@ -3550,11 +3562,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B124" t="n">
-        <v>22.66020584106445</v>
+        <v>22.66020202636719</v>
       </c>
       <c r="C124" t="n">
         <v>32.72999954223633</v>
@@ -3579,11 +3591,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B125" t="n">
-        <v>23.10329627990723</v>
+        <v>23.10330009460449</v>
       </c>
       <c r="C125" t="n">
         <v>33.36999893188477</v>
@@ -3608,11 +3620,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B126" t="n">
-        <v>23.35217094421387</v>
+        <v>23.3521785736084</v>
       </c>
       <c r="C126" t="n">
         <v>33.29000091552734</v>
@@ -3637,11 +3649,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B127" t="n">
-        <v>22.2508544921875</v>
+        <v>22.25085639953613</v>
       </c>
       <c r="C127" t="n">
         <v>31.71999931335449</v>
@@ -3666,11 +3678,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B128" t="n">
-        <v>22.4612979888916</v>
+        <v>22.46129417419434</v>
       </c>
       <c r="C128" t="n">
         <v>32.02000045776367</v>
@@ -3695,7 +3707,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B129" t="n">
@@ -3724,11 +3736,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B130" t="n">
-        <v>24.46362113952637</v>
+        <v>24.46361351013184</v>
       </c>
       <c r="C130" t="n">
         <v>34</v>
@@ -3753,11 +3765,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B131" t="n">
-        <v>22.98860359191895</v>
+        <v>22.98861503601074</v>
       </c>
       <c r="C131" t="n">
         <v>31.95000076293945</v>
@@ -3782,11 +3794,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B132" t="n">
-        <v>22.51922035217285</v>
+        <v>22.51922416687012</v>
       </c>
       <c r="C132" t="n">
         <v>30.95000076293945</v>
@@ -3811,11 +3823,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B133" t="n">
-        <v>23.23226547241211</v>
+        <v>23.23226737976074</v>
       </c>
       <c r="C133" t="n">
         <v>31.93000030517578</v>
@@ -3840,11 +3852,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B134" t="n">
-        <v>23.40689086914062</v>
+        <v>23.40689468383789</v>
       </c>
       <c r="C134" t="n">
         <v>32.16999816894531</v>
@@ -3869,7 +3881,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B135" t="n">
@@ -3898,11 +3910,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B136" t="n">
-        <v>27.29548072814941</v>
+        <v>27.29547691345215</v>
       </c>
       <c r="C136" t="n">
         <v>36.90999984741211</v>
@@ -3927,11 +3939,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B137" t="n">
-        <v>28.16071128845215</v>
+        <v>28.16070747375488</v>
       </c>
       <c r="C137" t="n">
         <v>38.08000183105469</v>
@@ -3956,11 +3968,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B138" t="n">
-        <v>24.40781211853027</v>
+        <v>24.40780830383301</v>
       </c>
       <c r="C138" t="n">
         <v>32.36000061035156</v>
@@ -3985,11 +3997,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B139" t="n">
-        <v>25.44114685058594</v>
+        <v>25.44114112854004</v>
       </c>
       <c r="C139" t="n">
         <v>33.72999954223633</v>
@@ -4014,11 +4026,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B140" t="n">
-        <v>22.48444938659668</v>
+        <v>22.48444747924805</v>
       </c>
       <c r="C140" t="n">
         <v>29.80999946594238</v>
@@ -4043,11 +4055,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B141" t="n">
-        <v>25.41852188110352</v>
+        <v>25.41851615905762</v>
       </c>
       <c r="C141" t="n">
         <v>33.70000076293945</v>
@@ -4072,11 +4084,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B142" t="n">
-        <v>25.61520195007324</v>
+        <v>25.61520385742188</v>
       </c>
       <c r="C142" t="n">
         <v>33.38999938964844</v>
@@ -4101,11 +4113,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B143" t="n">
-        <v>26.82731056213379</v>
+        <v>26.82730293273926</v>
       </c>
       <c r="C143" t="n">
         <v>34.97000122070312</v>
@@ -4130,11 +4142,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B144" t="n">
-        <v>30.5534496307373</v>
+        <v>30.55345153808594</v>
       </c>
       <c r="C144" t="n">
         <v>39.45999908447266</v>
@@ -4159,7 +4171,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B145" t="n">
@@ -4188,7 +4200,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B146" t="n">
@@ -4217,11 +4229,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B147" t="n">
-        <v>37.51253509521484</v>
+        <v>37.51254272460938</v>
       </c>
       <c r="C147" t="n">
         <v>47.97999954223633</v>
@@ -4246,11 +4258,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B148" t="n">
-        <v>38.90421676635742</v>
+        <v>38.90421295166016</v>
       </c>
       <c r="C148" t="n">
         <v>49.7599983215332</v>
@@ -4275,11 +4287,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B149" t="n">
-        <v>38.18492126464844</v>
+        <v>38.1849250793457</v>
       </c>
       <c r="C149" t="n">
         <v>48.84000015258789</v>
@@ -4304,11 +4316,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B150" t="n">
-        <v>41.56245803833008</v>
+        <v>41.56246185302734</v>
       </c>
       <c r="C150" t="n">
         <v>53.15999984741211</v>
@@ -4333,11 +4345,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B151" t="n">
-        <v>42.78557586669922</v>
+        <v>42.78557968139648</v>
       </c>
       <c r="C151" t="n">
         <v>54.22000122070312</v>
@@ -4362,11 +4374,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B152" t="n">
-        <v>44.14284133911133</v>
+        <v>44.14284515380859</v>
       </c>
       <c r="C152" t="n">
         <v>55.93999862670898</v>
@@ -4391,11 +4403,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B153" t="n">
-        <v>48.19097900390625</v>
+        <v>48.19099044799805</v>
       </c>
       <c r="C153" t="n">
         <v>61.06999969482422</v>
@@ -4420,7 +4432,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B154" t="n">
@@ -4449,11 +4461,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B155" t="n">
-        <v>36.30467224121094</v>
+        <v>36.30466079711914</v>
       </c>
       <c r="C155" t="n">
         <v>45.56999969482422</v>
@@ -4478,7 +4490,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B156" t="n">
@@ -4507,11 +4519,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B157" t="n">
-        <v>45.59174728393555</v>
+        <v>45.59173583984375</v>
       </c>
       <c r="C157" t="n">
         <v>56.79999923706055</v>
@@ -4536,11 +4548,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B158" t="n">
-        <v>45.47937393188477</v>
+        <v>45.47937774658203</v>
       </c>
       <c r="C158" t="n">
         <v>56.65999984741211</v>
@@ -4565,7 +4577,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B159" t="n">
@@ -4594,7 +4606,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B160" t="n">
@@ -4623,7 +4635,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B161" t="n">
@@ -4652,11 +4664,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B162" t="n">
-        <v>40.7464714050293</v>
+        <v>40.74646377563477</v>
       </c>
       <c r="C162" t="n">
         <v>50.41999816894531</v>
@@ -4681,11 +4693,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B163" t="n">
-        <v>48.5814208984375</v>
+        <v>48.58142471313477</v>
       </c>
       <c r="C163" t="n">
         <v>59.54999923706055</v>
@@ -4710,7 +4722,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B164" t="n">
@@ -4739,11 +4751,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B165" t="n">
-        <v>54.81421661376953</v>
+        <v>54.8142204284668</v>
       </c>
       <c r="C165" t="n">
         <v>67.19000244140625</v>
@@ -4768,11 +4780,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B166" t="n">
-        <v>57.25268173217773</v>
+        <v>57.2526969909668</v>
       </c>
       <c r="C166" t="n">
         <v>69.23000335693359</v>
@@ -4797,11 +4809,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B167" t="n">
-        <v>61.63576507568359</v>
+        <v>61.6357536315918</v>
       </c>
       <c r="C167" t="n">
         <v>74.52999877929688</v>
@@ -4826,7 +4838,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B168" t="n">
@@ -4855,7 +4867,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B169" t="n">
@@ -4884,11 +4896,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B170" t="n">
-        <v>81.07688903808594</v>
+        <v>81.07688140869141</v>
       </c>
       <c r="C170" t="n">
         <v>97.13999938964844</v>
@@ -4913,7 +4925,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B171" t="n">
@@ -4942,7 +4954,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B172" t="n">
@@ -4971,7 +4983,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B173" t="n">
@@ -5000,11 +5012,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B174" t="n">
-        <v>117.144172668457</v>
+        <v>117.1441650390625</v>
       </c>
       <c r="C174" t="n">
         <v>138.4199981689453</v>
@@ -5029,7 +5041,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B175" t="n">
@@ -5058,11 +5070,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B176" t="n">
-        <v>109.5021057128906</v>
+        <v>109.5021209716797</v>
       </c>
       <c r="C176" t="n">
         <v>129.3899993896484</v>
@@ -5087,11 +5099,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B177" t="n">
-        <v>111.685546875</v>
+        <v>111.6855545043945</v>
       </c>
       <c r="C177" t="n">
         <v>131.9700012207031</v>
@@ -5116,7 +5128,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B178" t="n">
@@ -5145,11 +5157,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B179" t="n">
-        <v>108.6030883789062</v>
+        <v>108.6030731201172</v>
       </c>
       <c r="C179" t="n">
         <v>126.9400024414062</v>
@@ -5174,11 +5186,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B180" t="n">
-        <v>87.97016906738281</v>
+        <v>87.97017669677734</v>
       </c>
       <c r="C180" t="n">
         <v>101.5699996948242</v>
@@ -5203,11 +5215,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B181" t="n">
-        <v>102.0183944702148</v>
+        <v>102.0183792114258</v>
       </c>
       <c r="C181" t="n">
         <v>117.7900009155273</v>
@@ -5232,11 +5244,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B182" t="n">
-        <v>79.0146484375</v>
+        <v>79.01466369628906</v>
       </c>
       <c r="C182" t="n">
         <v>91.23000335693359</v>
@@ -5261,11 +5273,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B183" t="n">
-        <v>89.51251220703125</v>
+        <v>89.51253509521484</v>
       </c>
       <c r="C183" t="n">
         <v>102.0699996948242</v>
@@ -5290,11 +5302,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B184" t="n">
-        <v>82.38275146484375</v>
+        <v>82.38275909423828</v>
       </c>
       <c r="C184" t="n">
         <v>93.94000244140625</v>
@@ -5319,11 +5331,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B185" t="n">
-        <v>73.40254974365234</v>
+        <v>73.40254211425781</v>
       </c>
       <c r="C185" t="n">
         <v>83.69999694824219</v>
@@ -5348,7 +5360,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B186" t="n">
@@ -5377,7 +5389,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B187" t="n">
@@ -5406,11 +5418,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B188" t="n">
-        <v>65.69525909423828</v>
+        <v>65.69525146484375</v>
       </c>
       <c r="C188" t="n">
         <v>74.19000244140625</v>
@@ -5435,7 +5447,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B189" t="n">
@@ -5464,11 +5476,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B190" t="n">
-        <v>81.14156341552734</v>
+        <v>81.14157104492188</v>
       </c>
       <c r="C190" t="n">
         <v>90.80000305175781</v>
@@ -5493,7 +5505,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B191" t="n">
@@ -5522,11 +5534,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B192" t="n">
-        <v>80.58625793457031</v>
+        <v>80.58625030517578</v>
       </c>
       <c r="C192" t="n">
         <v>89.33000183105469</v>
@@ -5551,11 +5563,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B193" t="n">
-        <v>77.2574462890625</v>
+        <v>77.25743865966797</v>
       </c>
       <c r="C193" t="n">
         <v>85.63999938964844</v>
@@ -5580,7 +5592,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B194" t="n">
@@ -5609,11 +5621,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B195" t="n">
-        <v>95.26167297363281</v>
+        <v>95.26168060302734</v>
       </c>
       <c r="C195" t="n">
         <v>104.7900009155273</v>
@@ -5638,11 +5650,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B196" t="n">
-        <v>96.69801330566406</v>
+        <v>96.69802093505859</v>
       </c>
       <c r="C196" t="n">
         <v>106.370002746582</v>
@@ -5667,7 +5679,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B197" t="n">
@@ -5696,7 +5708,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B198" t="n">
@@ -5725,7 +5737,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B199" t="n">
@@ -5754,11 +5766,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B200" t="n">
-        <v>120.0563125610352</v>
+        <v>120.0563049316406</v>
       </c>
       <c r="C200" t="n">
         <v>130.9199981689453</v>
@@ -5783,7 +5795,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B201" t="n">
@@ -5812,7 +5824,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B202" t="n">
@@ -5841,7 +5853,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B203" t="n">
@@ -5870,7 +5882,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B204" t="n">
@@ -5899,7 +5911,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B205" t="n">
@@ -5928,7 +5940,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B206" t="n">
@@ -5957,7 +5969,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B207" t="n">
@@ -5986,11 +5998,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B208" t="n">
-        <v>133.2020568847656</v>
+        <v>133.2020263671875</v>
       </c>
       <c r="C208" t="n">
         <v>142.3600006103516</v>
@@ -6015,11 +6027,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B209" t="n">
-        <v>143.2792205810547</v>
+        <v>143.2792053222656</v>
       </c>
       <c r="C209" t="n">
         <v>153.1300048828125</v>
@@ -6044,11 +6056,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B210" t="n">
-        <v>157.7687530517578</v>
+        <v>157.7687377929688</v>
       </c>
       <c r="C210" t="n">
         <v>167.75</v>
@@ -6073,11 +6085,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B211" t="n">
-        <v>179.7200164794922</v>
+        <v>179.7199859619141</v>
       </c>
       <c r="C211" t="n">
         <v>191.0899963378906</v>
@@ -6102,11 +6114,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B212" t="n">
-        <v>162.1609039306641</v>
+        <v>162.160888671875</v>
       </c>
       <c r="C212" t="n">
         <v>172.4199981689453</v>
@@ -6131,11 +6143,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B213" t="n">
-        <v>166.5718383789062</v>
+        <v>166.5718078613281</v>
       </c>
       <c r="C213" t="n">
         <v>177.1100006103516</v>
@@ -6160,7 +6172,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B214" t="n">
@@ -6189,7 +6201,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B215" t="n">
@@ -6218,11 +6230,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B216" t="n">
-        <v>125.8103713989258</v>
+        <v>125.8103561401367</v>
       </c>
       <c r="C216" t="n">
         <v>131.7100067138672</v>
@@ -6247,11 +6259,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B217" t="n">
-        <v>132.5445709228516</v>
+        <v>132.5445556640625</v>
       </c>
       <c r="C217" t="n">
         <v>138.7599945068359</v>
@@ -6276,7 +6288,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B218" t="n">
@@ -6305,7 +6317,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B219" t="n">
@@ -6334,11 +6346,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B220" t="n">
-        <v>164.7182159423828</v>
+        <v>164.7182006835938</v>
       </c>
       <c r="C220" t="n">
         <v>171.3999938964844</v>
@@ -6363,7 +6375,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B221" t="n">
@@ -6392,7 +6404,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B222" t="n">
@@ -6421,11 +6433,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B223" t="n">
-        <v>141.9608459472656</v>
+        <v>141.9608612060547</v>
       </c>
       <c r="C223" t="n">
         <v>146.4199981689453</v>
@@ -6450,11 +6462,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B224" t="n">
-        <v>149.4457397460938</v>
+        <v>149.4457550048828</v>
       </c>
       <c r="C224" t="n">
         <v>154.1399993896484</v>
@@ -6479,7 +6491,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B225" t="n">
@@ -6508,7 +6520,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B226" t="n">
@@ -6537,11 +6549,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B227" t="n">
-        <v>112.7837982177734</v>
+        <v>112.783805847168</v>
       </c>
       <c r="C227" t="n">
         <v>114.9899978637695</v>
@@ -6566,7 +6578,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B228" t="n">
@@ -6595,7 +6607,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B229" t="n">
@@ -6624,7 +6636,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B230" t="n">
@@ -6653,7 +6665,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B231" t="n">
@@ -6682,7 +6694,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B232" t="n">
@@ -6711,32 +6723,32 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B233" t="n">
-        <v>119.2699966430664</v>
+        <v>117.2099990844727</v>
       </c>
       <c r="C233" t="n">
-        <v>119.2699966430664</v>
+        <v>117.2099990844727</v>
       </c>
       <c r="D233" t="n">
-        <v>59369700</v>
+        <v>64655400</v>
       </c>
       <c r="E233" t="n">
         <v>4.46</v>
       </c>
       <c r="F233" t="n">
-        <v>26.74215171369202</v>
+        <v>26.28026885302078</v>
       </c>
       <c r="G233" t="n">
         <v>750625114</v>
       </c>
       <c r="H233" t="n">
-        <v>89527054826.98134</v>
+        <v>87980768924.72218</v>
       </c>
       <c r="I233" t="n">
-        <v>0.07909367658061064</v>
+        <v>0.08613540740125036</v>
       </c>
     </row>
   </sheetData>
@@ -6768,75 +6780,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6872,13 +6884,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6914,13 +6926,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6956,13 +6968,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6989,7 +7001,7 @@
       <c r="I5" t="n">
         <v>-1.06</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K5" t="n">
@@ -7002,13 +7014,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7035,7 +7047,7 @@
       <c r="I6" t="n">
         <v>-0.6100000000000001</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K6" t="n">
@@ -7048,13 +7060,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7081,7 +7093,7 @@
       <c r="I7" t="n">
         <v>0.12</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K7" t="n">
@@ -7094,13 +7106,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7127,7 +7139,7 @@
       <c r="I8" t="n">
         <v>-0.3200000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K8" t="n">
@@ -7140,13 +7152,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7173,7 +7185,7 @@
       <c r="I9" t="n">
         <v>-0.34</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K9" t="n">
@@ -7186,13 +7198,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7219,7 +7231,7 @@
       <c r="I10" t="n">
         <v>-0.3200000000000001</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K10" t="n">
@@ -7232,13 +7244,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7265,7 +7277,7 @@
       <c r="I11" t="n">
         <v>-0.64</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K11" t="n">
@@ -7278,13 +7290,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7311,7 +7323,7 @@
       <c r="I12" t="n">
         <v>0.16</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K12" t="n">
@@ -7324,13 +7336,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7357,7 +7369,7 @@
       <c r="I13" t="n">
         <v>0.4</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K13" t="n">
@@ -7370,13 +7382,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7403,7 +7415,7 @@
       <c r="I14" t="n">
         <v>0.5800000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K14" t="n">
@@ -7416,13 +7428,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7449,7 +7461,7 @@
       <c r="I15" t="n">
         <v>1.08</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K15" t="n">
@@ -7462,13 +7474,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7495,7 +7507,7 @@
       <c r="I16" t="n">
         <v>1.13</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="K16" t="n">
@@ -7508,13 +7520,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7541,7 +7553,7 @@
       <c r="I17" t="n">
         <v>1.98</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="K17" t="n">
@@ -7554,13 +7566,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7587,7 +7599,7 @@
       <c r="I18" t="n">
         <v>2.13</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K18" t="n">
@@ -7600,13 +7612,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41737</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7633,7 +7645,7 @@
       <c r="I19" t="n">
         <v>2.62</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K19" t="n">
@@ -7646,13 +7658,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7679,7 +7691,7 @@
       <c r="I20" t="n">
         <v>2.74</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K20" t="n">
@@ -7692,13 +7704,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -7725,7 +7737,7 @@
       <c r="I21" t="n">
         <v>2.59</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K21" t="n">
@@ -7738,13 +7750,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -7771,7 +7783,7 @@
       <c r="I22" t="n">
         <v>3.15</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K22" t="n">
@@ -7784,13 +7796,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7817,7 +7829,7 @@
       <c r="I23" t="n">
         <v>2.51</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K23" t="n">
@@ -7830,13 +7842,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7863,7 +7875,7 @@
       <c r="I24" t="n">
         <v>1.7</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K24" t="n">
@@ -7876,13 +7888,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7909,7 +7921,7 @@
       <c r="I25" t="n">
         <v>1.04</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K25" t="n">
@@ -7922,13 +7934,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7955,7 +7967,7 @@
       <c r="I26" t="n">
         <v>0.27</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K26" t="n">
@@ -7968,13 +7980,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8001,7 +8013,7 @@
       <c r="I27" t="n">
         <v>0.36</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K27" t="n">
@@ -8014,13 +8026,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8047,7 +8059,7 @@
       <c r="I28" t="n">
         <v>1.23</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="K28" t="n">
@@ -8060,13 +8072,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8093,7 +8105,7 @@
       <c r="I29" t="n">
         <v>1.55</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K29" t="n">
@@ -8106,13 +8118,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8139,7 +8151,7 @@
       <c r="I30" t="n">
         <v>2.01</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="K30" t="n">
@@ -8152,13 +8164,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8185,7 +8197,7 @@
       <c r="I31" t="n">
         <v>2.22</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="K31" t="n">
@@ -8198,13 +8210,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8231,7 +8243,7 @@
       <c r="I32" t="n">
         <v>2.31</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="K32" t="n">
@@ -8244,13 +8256,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8277,7 +8289,7 @@
       <c r="I33" t="n">
         <v>2.18</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="K33" t="n">
@@ -8290,13 +8302,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8323,7 +8335,7 @@
       <c r="I34" t="n">
         <v>2.02</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="K34" t="n">
@@ -8336,13 +8348,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8369,7 +8381,7 @@
       <c r="I35" t="n">
         <v>2.6</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="K35" t="n">
@@ -8382,13 +8394,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8415,7 +8427,7 @@
       <c r="I36" t="n">
         <v>2.68</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="K36" t="n">
@@ -8428,13 +8440,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8461,7 +8473,7 @@
       <c r="I37" t="n">
         <v>2.24</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="K37" t="n">
@@ -8474,13 +8486,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8507,7 +8519,7 @@
       <c r="I38" t="n">
         <v>2.42</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K38" t="n">
@@ -8520,13 +8532,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8553,7 +8565,7 @@
       <c r="I39" t="n">
         <v>1.78</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="K39" t="n">
@@ -8566,13 +8578,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8599,7 +8611,7 @@
       <c r="I40" t="n">
         <v>2.29</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="K40" t="n">
@@ -8612,13 +8624,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8645,7 +8657,7 @@
       <c r="I41" t="n">
         <v>3.02</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="K41" t="n">
@@ -8658,13 +8670,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8691,7 +8703,7 @@
       <c r="I42" t="n">
         <v>0.73</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="K42" t="n">
@@ -8704,13 +8716,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -8737,7 +8749,7 @@
       <c r="I43" t="n">
         <v>1.09</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="K43" t="n">
@@ -8750,13 +8762,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -8783,7 +8795,7 @@
       <c r="I44" t="n">
         <v>1.07</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="K44" t="n">
@@ -8796,13 +8808,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8829,7 +8841,7 @@
       <c r="I45" t="n">
         <v>1.5</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K45" t="n">
@@ -8842,13 +8854,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8875,7 +8887,7 @@
       <c r="I46" t="n">
         <v>5.54</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="K46" t="n">
@@ -8888,13 +8900,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8921,7 +8933,7 @@
       <c r="I47" t="n">
         <v>6.550000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K47" t="n">
@@ -8934,13 +8946,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8967,7 +8979,7 @@
       <c r="I48" t="n">
         <v>7.359999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K48" t="n">
@@ -8980,13 +8992,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9013,7 +9025,7 @@
       <c r="I49" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K49" t="n">
@@ -9026,13 +9038,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9059,7 +9071,7 @@
       <c r="I50" t="n">
         <v>7.33</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K50" t="n">
@@ -9072,13 +9084,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9105,7 +9117,7 @@
       <c r="I51" t="n">
         <v>5.47</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K51" t="n">
@@ -9118,13 +9130,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9151,7 +9163,7 @@
       <c r="I52" t="n">
         <v>3.53</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K52" t="n">
@@ -9164,13 +9176,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9197,7 +9209,7 @@
       <c r="I53" t="n">
         <v>2.36</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K53" t="n">
@@ -9210,13 +9222,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9243,7 +9255,7 @@
       <c r="I54" t="n">
         <v>0.8099999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K54" t="n">
@@ -9256,13 +9268,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9289,7 +9301,7 @@
       <c r="I55" t="n">
         <v>1.64</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K55" t="n">
@@ -9302,13 +9314,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9335,7 +9347,7 @@
       <c r="I56" t="n">
         <v>2.37</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K56" t="n">
@@ -9348,13 +9360,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9381,7 +9393,7 @@
       <c r="I57" t="n">
         <v>1.84</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K57" t="n">
@@ -9394,13 +9406,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9427,7 +9439,7 @@
       <c r="I58" t="n">
         <v>2.84</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K58" t="n">
@@ -9440,13 +9452,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9473,7 +9485,7 @@
       <c r="I59" t="n">
         <v>2.63</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K59" t="n">
@@ -9486,13 +9498,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9519,7 +9531,7 @@
       <c r="I60" t="n">
         <v>2.92</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K60" t="n">
@@ -9532,13 +9544,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9565,7 +9577,7 @@
       <c r="I61" t="n">
         <v>3.62</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="K61" t="n">
@@ -9578,13 +9590,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9611,7 +9623,7 @@
       <c r="I62" t="n">
         <v>3.31</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K62" t="n">
@@ -9624,13 +9636,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9657,7 +9669,7 @@
       <c r="I63" t="n">
         <v>3.71</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="K63" t="n">
@@ -9670,13 +9682,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9703,7 +9715,7 @@
       <c r="I64" t="n">
         <v>3.49</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="K64" t="n">
@@ -9716,13 +9728,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -9749,7 +9761,7 @@
       <c r="I65" t="n">
         <v>3.87</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="K65" t="n">
@@ -9762,13 +9774,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9795,7 +9807,7 @@
       <c r="I66" t="n">
         <v>3.899999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="K66" t="n">
@@ -9808,13 +9820,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -9841,7 +9853,7 @@
       <c r="I67" t="n">
         <v>4.46</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K67" t="n">
@@ -9879,57 +9891,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C2" t="n">
@@ -9959,10 +9971,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C3" t="n">
@@ -9992,10 +10004,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40592</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C4" t="n">
@@ -10025,10 +10037,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C5" t="n">
@@ -10062,10 +10074,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C6" t="n">
@@ -10099,10 +10111,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C7" t="n">
@@ -10132,10 +10144,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C8" t="n">
@@ -10165,10 +10177,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C9" t="n">
@@ -10198,10 +10210,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C10" t="n">
@@ -10231,10 +10243,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41327</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C11" t="n">
@@ -10264,10 +10276,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C12" t="n">
@@ -10297,10 +10309,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C13" t="n">
@@ -10330,10 +10342,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41586</v>
       </c>
       <c r="C14" t="n">
@@ -10363,10 +10375,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41691</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="C15" t="n">
@@ -10396,10 +10408,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C16" t="n">
@@ -10429,10 +10441,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C17" t="n">
@@ -10462,10 +10474,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C18" t="n">
@@ -10495,10 +10507,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42059</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C19" t="n">
@@ -10528,10 +10540,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C20" t="n">
@@ -10561,10 +10573,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C21" t="n">
@@ -10594,10 +10606,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C22" t="n">
@@ -10627,10 +10639,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42419</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C23" t="n">
@@ -10660,10 +10672,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C24" t="n">
@@ -10693,10 +10705,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C25" t="n">
@@ -10726,10 +10738,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42676</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42682</v>
       </c>
       <c r="C26" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42783</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C27" t="n">
@@ -10792,10 +10804,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42858</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42864</v>
       </c>
       <c r="C28" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C29" t="n">
@@ -10858,10 +10870,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43046</v>
       </c>
       <c r="C30" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43153</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C31" t="n">
@@ -10924,10 +10936,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43222</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43228</v>
       </c>
       <c r="C32" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43314</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43320</v>
       </c>
       <c r="C33" t="n">
@@ -10990,10 +11002,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43411</v>
       </c>
       <c r="C34" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43518</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="C35" t="n">
@@ -11056,10 +11068,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43588</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C36" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C37" t="n">
@@ -11122,10 +11134,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="C38" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="C39" t="n">
@@ -11196,10 +11208,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="C40" t="n">
@@ -11233,10 +11245,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44251</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C41" t="n">
@@ -11266,10 +11278,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C42" t="n">
@@ -11299,10 +11311,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C43" t="n">
@@ -11332,10 +11344,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C44" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C45" t="n">
@@ -11398,10 +11410,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C46" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C47" t="n">
@@ -11464,10 +11476,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C48" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C49" t="n">
@@ -11530,10 +11542,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C50" t="n">
@@ -11563,10 +11575,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45135</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C51" t="n">
@@ -11596,10 +11608,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C52" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C53" t="n">
@@ -11662,10 +11674,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C54" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45499</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C55" t="n">
@@ -11728,10 +11740,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C56" t="n">
@@ -11761,10 +11773,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45709</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="C57" t="n">
@@ -11794,10 +11806,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45772</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C58" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="C59" t="n">
@@ -11860,10 +11872,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="C60" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="C61" t="n">
@@ -11926,10 +11938,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="C62" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C63" t="n">
@@ -12010,12 +12022,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BX.xlsx
+++ b/salidas/empresas/BX.xlsx
@@ -498,7 +498,7 @@
         <v>39263</v>
       </c>
       <c r="B2" t="n">
-        <v>10.64566326141357</v>
+        <v>10.64565849304199</v>
       </c>
       <c r="C2" t="n">
         <v>28.72423934936523</v>
@@ -517,7 +517,7 @@
         <v>39294</v>
       </c>
       <c r="B3" t="n">
-        <v>8.73256778717041</v>
+        <v>8.732568740844727</v>
       </c>
       <c r="C3" t="n">
         <v>23.56231689453125</v>
@@ -555,7 +555,7 @@
         <v>39355</v>
       </c>
       <c r="B5" t="n">
-        <v>9.121734619140625</v>
+        <v>9.121732711791992</v>
       </c>
       <c r="C5" t="n">
         <v>24.61236572265625</v>
@@ -574,7 +574,7 @@
         <v>39386</v>
       </c>
       <c r="B6" t="n">
-        <v>9.249029159545898</v>
+        <v>9.249031066894531</v>
       </c>
       <c r="C6" t="n">
         <v>24.95583915710449</v>
@@ -593,7 +593,7 @@
         <v>39416</v>
       </c>
       <c r="B7" t="n">
-        <v>8.118389129638672</v>
+        <v>8.118385314941406</v>
       </c>
       <c r="C7" t="n">
         <v>21.58979415893555</v>
@@ -612,7 +612,7 @@
         <v>39447</v>
       </c>
       <c r="B8" t="n">
-        <v>8.16635799407959</v>
+        <v>8.166361808776855</v>
       </c>
       <c r="C8" t="n">
         <v>21.71736907958984</v>
@@ -631,7 +631,7 @@
         <v>39478</v>
       </c>
       <c r="B9" t="n">
-        <v>6.77147102355957</v>
+        <v>6.771470546722412</v>
       </c>
       <c r="C9" t="n">
         <v>18.00785064697266</v>
@@ -650,7 +650,7 @@
         <v>39507</v>
       </c>
       <c r="B10" t="n">
-        <v>6.088790893554688</v>
+        <v>6.088790416717529</v>
       </c>
       <c r="C10" t="n">
         <v>16.19234466552734</v>
@@ -669,7 +669,7 @@
         <v>39538</v>
       </c>
       <c r="B11" t="n">
-        <v>5.97084379196167</v>
+        <v>5.970845222473145</v>
       </c>
       <c r="C11" t="n">
         <v>15.58390617370605</v>
@@ -688,7 +688,7 @@
         <v>39568</v>
       </c>
       <c r="B12" t="n">
-        <v>7.019876003265381</v>
+        <v>7.019878387451172</v>
       </c>
       <c r="C12" t="n">
         <v>18.32188415527344</v>
@@ -707,7 +707,7 @@
         <v>39599</v>
       </c>
       <c r="B13" t="n">
-        <v>7.438689708709717</v>
+        <v>7.438685894012451</v>
       </c>
       <c r="C13" t="n">
         <v>19.10696792602539</v>
@@ -745,7 +745,7 @@
         <v>39660</v>
       </c>
       <c r="B15" t="n">
-        <v>7.094835758209229</v>
+        <v>7.094831943511963</v>
       </c>
       <c r="C15" t="n">
         <v>18.2237491607666</v>
@@ -764,7 +764,7 @@
         <v>39691</v>
       </c>
       <c r="B16" t="n">
-        <v>6.952335357666016</v>
+        <v>6.952334880828857</v>
       </c>
       <c r="C16" t="n">
         <v>17.5466136932373</v>
@@ -783,7 +783,7 @@
         <v>39721</v>
       </c>
       <c r="B17" t="n">
-        <v>5.964700222015381</v>
+        <v>5.964697360992432</v>
       </c>
       <c r="C17" t="n">
         <v>15.05397415161133</v>
@@ -802,7 +802,7 @@
         <v>39752</v>
       </c>
       <c r="B18" t="n">
-        <v>3.553936004638672</v>
+        <v>3.553935289382935</v>
       </c>
       <c r="C18" t="n">
         <v>8.969577789306641</v>
@@ -821,7 +821,7 @@
         <v>39782</v>
       </c>
       <c r="B19" t="n">
-        <v>2.553218603134155</v>
+        <v>2.553218841552734</v>
       </c>
       <c r="C19" t="n">
         <v>6.143278121948242</v>
@@ -859,7 +859,7 @@
         <v>39844</v>
       </c>
       <c r="B21" t="n">
-        <v>1.839459776878357</v>
+        <v>1.839459896087646</v>
       </c>
       <c r="C21" t="n">
         <v>4.425908088684082</v>
@@ -878,7 +878,7 @@
         <v>39872</v>
       </c>
       <c r="B22" t="n">
-        <v>1.986289620399475</v>
+        <v>1.986289978027344</v>
       </c>
       <c r="C22" t="n">
         <v>4.779194831848145</v>
@@ -897,7 +897,7 @@
         <v>39903</v>
       </c>
       <c r="B23" t="n">
-        <v>2.957001924514771</v>
+        <v>2.957002878189087</v>
       </c>
       <c r="C23" t="n">
         <v>7.114818096160889</v>
@@ -916,7 +916,7 @@
         <v>39933</v>
       </c>
       <c r="B24" t="n">
-        <v>3.992974042892456</v>
+        <v>3.992973804473877</v>
       </c>
       <c r="C24" t="n">
         <v>9.607458114624023</v>
@@ -935,7 +935,7 @@
         <v>39964</v>
       </c>
       <c r="B25" t="n">
-        <v>4.586256504058838</v>
+        <v>4.586257457733154</v>
       </c>
       <c r="C25" t="n">
         <v>10.74582862854004</v>
@@ -954,7 +954,7 @@
         <v>39994</v>
       </c>
       <c r="B26" t="n">
-        <v>4.414534568786621</v>
+        <v>4.414534091949463</v>
       </c>
       <c r="C26" t="n">
         <v>10.34347438812256</v>
@@ -973,7 +973,7 @@
         <v>40025</v>
       </c>
       <c r="B27" t="n">
-        <v>4.716098308563232</v>
+        <v>4.7160964012146</v>
       </c>
       <c r="C27" t="n">
         <v>11.050048828125</v>
@@ -1011,7 +1011,7 @@
         <v>40086</v>
       </c>
       <c r="B29" t="n">
-        <v>6.086868762969971</v>
+        <v>6.086865425109863</v>
       </c>
       <c r="C29" t="n">
         <v>13.93523120880127</v>
@@ -1030,7 +1030,7 @@
         <v>40117</v>
       </c>
       <c r="B30" t="n">
-        <v>5.752519607543945</v>
+        <v>5.752518177032471</v>
       </c>
       <c r="C30" t="n">
         <v>13.16977405548096</v>
@@ -1049,7 +1049,7 @@
         <v>40147</v>
       </c>
       <c r="B31" t="n">
-        <v>6.062180042266846</v>
+        <v>6.062177658081055</v>
       </c>
       <c r="C31" t="n">
         <v>13.58194255828857</v>
@@ -1068,7 +1068,7 @@
         <v>40178</v>
       </c>
       <c r="B32" t="n">
-        <v>5.746806621551514</v>
+        <v>5.746803283691406</v>
       </c>
       <c r="C32" t="n">
         <v>12.87536811828613</v>
@@ -1087,7 +1087,7 @@
         <v>40209</v>
       </c>
       <c r="B33" t="n">
-        <v>5.313168048858643</v>
+        <v>5.313166618347168</v>
       </c>
       <c r="C33" t="n">
         <v>11.90382671356201</v>
@@ -1106,7 +1106,7 @@
         <v>40237</v>
       </c>
       <c r="B34" t="n">
-        <v>6.123501777648926</v>
+        <v>6.123500823974609</v>
       </c>
       <c r="C34" t="n">
         <v>13.71933269500732</v>
@@ -1125,7 +1125,7 @@
         <v>40268</v>
       </c>
       <c r="B35" t="n">
-        <v>6.258786678314209</v>
+        <v>6.258790016174316</v>
       </c>
       <c r="C35" t="n">
         <v>13.73896026611328</v>
@@ -1144,7 +1144,7 @@
         <v>40298</v>
       </c>
       <c r="B36" t="n">
-        <v>6.249846935272217</v>
+        <v>6.2498459815979</v>
       </c>
       <c r="C36" t="n">
         <v>13.71933269500732</v>
@@ -1163,7 +1163,7 @@
         <v>40329</v>
       </c>
       <c r="B37" t="n">
-        <v>4.798001289367676</v>
+        <v>4.797999382019043</v>
       </c>
       <c r="C37" t="n">
         <v>10.45142269134521</v>
@@ -1201,7 +1201,7 @@
         <v>40390</v>
       </c>
       <c r="B39" t="n">
-        <v>5.023258686065674</v>
+        <v>5.023257732391357</v>
       </c>
       <c r="C39" t="n">
         <v>10.94209957122803</v>
@@ -1220,7 +1220,7 @@
         <v>40421</v>
       </c>
       <c r="B40" t="n">
-        <v>4.587451934814453</v>
+        <v>4.587453365325928</v>
       </c>
       <c r="C40" t="n">
         <v>9.901865005493164</v>
@@ -1245,7 +1245,7 @@
         <v>40451</v>
       </c>
       <c r="B41" t="n">
-        <v>5.769554138183594</v>
+        <v>5.769551277160645</v>
       </c>
       <c r="C41" t="n">
         <v>12.4533863067627</v>
@@ -1270,7 +1270,7 @@
         <v>40482</v>
       </c>
       <c r="B42" t="n">
-        <v>6.12872838973999</v>
+        <v>6.128730297088623</v>
       </c>
       <c r="C42" t="n">
         <v>13.22865581512451</v>
@@ -1295,7 +1295,7 @@
         <v>40512</v>
       </c>
       <c r="B43" t="n">
-        <v>5.861732006072998</v>
+        <v>5.861734390258789</v>
       </c>
       <c r="C43" t="n">
         <v>12.56133460998535</v>
@@ -1320,7 +1320,7 @@
         <v>40543</v>
       </c>
       <c r="B44" t="n">
-        <v>6.479964733123779</v>
+        <v>6.479963779449463</v>
       </c>
       <c r="C44" t="n">
         <v>13.88616275787354</v>
@@ -1345,7 +1345,7 @@
         <v>40574</v>
       </c>
       <c r="B45" t="n">
-        <v>7.203522682189941</v>
+        <v>7.203522205352783</v>
       </c>
       <c r="C45" t="n">
         <v>15.43670272827148</v>
@@ -1370,7 +1370,7 @@
         <v>40602</v>
       </c>
       <c r="B46" t="n">
-        <v>8.151474952697754</v>
+        <v>8.15147590637207</v>
       </c>
       <c r="C46" t="n">
         <v>17.46810531616211</v>
@@ -1395,7 +1395,7 @@
         <v>40633</v>
       </c>
       <c r="B47" t="n">
-        <v>8.340094566345215</v>
+        <v>8.340092658996582</v>
       </c>
       <c r="C47" t="n">
         <v>17.5466136932373</v>
@@ -1420,7 +1420,7 @@
         <v>40663</v>
       </c>
       <c r="B48" t="n">
-        <v>8.834528923034668</v>
+        <v>8.834526062011719</v>
       </c>
       <c r="C48" t="n">
         <v>18.58684921264648</v>
@@ -1445,7 +1445,7 @@
         <v>40694</v>
       </c>
       <c r="B49" t="n">
-        <v>8.132999420166016</v>
+        <v>8.133001327514648</v>
       </c>
       <c r="C49" t="n">
         <v>16.91854858398438</v>
@@ -1470,7 +1470,7 @@
         <v>40724</v>
       </c>
       <c r="B50" t="n">
-        <v>7.812207221984863</v>
+        <v>7.812207698822021</v>
       </c>
       <c r="C50" t="n">
         <v>16.2512264251709</v>
@@ -1495,7 +1495,7 @@
         <v>40755</v>
       </c>
       <c r="B51" t="n">
-        <v>7.835797786712646</v>
+        <v>7.835796356201172</v>
       </c>
       <c r="C51" t="n">
         <v>16.30029487609863</v>
@@ -1520,7 +1520,7 @@
         <v>40786</v>
       </c>
       <c r="B52" t="n">
-        <v>6.52064323425293</v>
+        <v>6.520643711090088</v>
       </c>
       <c r="C52" t="n">
         <v>13.45436668395996</v>
@@ -1545,7 +1545,7 @@
         <v>40816</v>
       </c>
       <c r="B53" t="n">
-        <v>5.697836399078369</v>
+        <v>5.697835445404053</v>
       </c>
       <c r="C53" t="n">
         <v>11.75662422180176</v>
@@ -1570,7 +1570,7 @@
         <v>40847</v>
       </c>
       <c r="B54" t="n">
-        <v>6.996255874633789</v>
+        <v>6.996257781982422</v>
       </c>
       <c r="C54" t="n">
         <v>14.4357213973999</v>
@@ -1595,7 +1595,7 @@
         <v>40877</v>
       </c>
       <c r="B55" t="n">
-        <v>6.579293727874756</v>
+        <v>6.579288959503174</v>
       </c>
       <c r="C55" t="n">
         <v>13.47399425506592</v>
@@ -1620,7 +1620,7 @@
         <v>40908</v>
       </c>
       <c r="B56" t="n">
-        <v>6.713461875915527</v>
+        <v>6.713464260101318</v>
       </c>
       <c r="C56" t="n">
         <v>13.74877262115479</v>
@@ -1645,7 +1645,7 @@
         <v>40939</v>
       </c>
       <c r="B57" t="n">
-        <v>7.576007843017578</v>
+        <v>7.576008796691895</v>
       </c>
       <c r="C57" t="n">
         <v>15.51521110534668</v>
@@ -1697,7 +1697,7 @@
         <v>40999</v>
       </c>
       <c r="B59" t="n">
-        <v>7.750629901885986</v>
+        <v>7.750630378723145</v>
       </c>
       <c r="C59" t="n">
         <v>15.64278697967529</v>
@@ -1724,7 +1724,7 @@
         <v>41029</v>
       </c>
       <c r="B60" t="n">
-        <v>6.593387603759766</v>
+        <v>6.593384742736816</v>
       </c>
       <c r="C60" t="n">
         <v>13.30716419219971</v>
@@ -1751,7 +1751,7 @@
         <v>41060</v>
       </c>
       <c r="B61" t="n">
-        <v>5.900765419006348</v>
+        <v>5.900764465332031</v>
       </c>
       <c r="C61" t="n">
         <v>11.815505027771</v>
@@ -1778,7 +1778,7 @@
         <v>41090</v>
       </c>
       <c r="B62" t="n">
-        <v>6.405564308166504</v>
+        <v>6.405566215515137</v>
       </c>
       <c r="C62" t="n">
         <v>12.8262996673584</v>
@@ -1805,7 +1805,7 @@
         <v>41121</v>
       </c>
       <c r="B63" t="n">
-        <v>6.787842273712158</v>
+        <v>6.787841796875</v>
       </c>
       <c r="C63" t="n">
         <v>13.59175682067871</v>
@@ -1832,7 +1832,7 @@
         <v>41152</v>
       </c>
       <c r="B64" t="n">
-        <v>6.659877300262451</v>
+        <v>6.659878253936768</v>
       </c>
       <c r="C64" t="n">
         <v>13.23846912384033</v>
@@ -1859,7 +1859,7 @@
         <v>41182</v>
       </c>
       <c r="B65" t="n">
-        <v>7.049894332885742</v>
+        <v>7.049890995025635</v>
       </c>
       <c r="C65" t="n">
         <v>14.01373863220215</v>
@@ -1886,7 +1886,7 @@
         <v>41213</v>
       </c>
       <c r="B66" t="n">
-        <v>7.583080291748047</v>
+        <v>7.583078861236572</v>
       </c>
       <c r="C66" t="n">
         <v>15.07360172271729</v>
@@ -1913,7 +1913,7 @@
         <v>41243</v>
       </c>
       <c r="B67" t="n">
-        <v>7.302669525146484</v>
+        <v>7.30266809463501</v>
       </c>
       <c r="C67" t="n">
         <v>14.41609382629395</v>
@@ -1942,7 +1942,7 @@
         <v>41274</v>
       </c>
       <c r="B68" t="n">
-        <v>7.750074863433838</v>
+        <v>7.750073432922363</v>
       </c>
       <c r="C68" t="n">
         <v>15.29931259155273</v>
@@ -1971,7 +1971,7 @@
         <v>41305</v>
       </c>
       <c r="B69" t="n">
-        <v>9.196682929992676</v>
+        <v>9.196686744689941</v>
       </c>
       <c r="C69" t="n">
         <v>18.15505409240723</v>
@@ -2000,7 +2000,7 @@
         <v>41333</v>
       </c>
       <c r="B70" t="n">
-        <v>9.612118721008301</v>
+        <v>9.612116813659668</v>
       </c>
       <c r="C70" t="n">
         <v>18.5475959777832</v>
@@ -2029,7 +2029,7 @@
         <v>41364</v>
       </c>
       <c r="B71" t="n">
-        <v>10.05966663360596</v>
+        <v>10.05966377258301</v>
       </c>
       <c r="C71" t="n">
         <v>19.41118621826172</v>
@@ -2087,7 +2087,7 @@
         <v>41425</v>
       </c>
       <c r="B73" t="n">
-        <v>11.29745101928711</v>
+        <v>11.29745292663574</v>
       </c>
       <c r="C73" t="n">
         <v>21.48184585571289</v>
@@ -2116,7 +2116,7 @@
         <v>41455</v>
       </c>
       <c r="B74" t="n">
-        <v>10.86908626556396</v>
+        <v>10.86908721923828</v>
       </c>
       <c r="C74" t="n">
         <v>20.66732025146484</v>
@@ -2145,7 +2145,7 @@
         <v>41486</v>
       </c>
       <c r="B75" t="n">
-        <v>11.75188827514648</v>
+        <v>11.75189018249512</v>
       </c>
       <c r="C75" t="n">
         <v>22.12953948974609</v>
@@ -2174,7 +2174,7 @@
         <v>41517</v>
       </c>
       <c r="B76" t="n">
-        <v>11.38187026977539</v>
+        <v>11.38187122344971</v>
       </c>
       <c r="C76" t="n">
         <v>21.43277740478516</v>
@@ -2203,7 +2203,7 @@
         <v>41547</v>
       </c>
       <c r="B77" t="n">
-        <v>12.97137260437012</v>
+        <v>12.97137546539307</v>
       </c>
       <c r="C77" t="n">
         <v>24.42590713500977</v>
@@ -2232,7 +2232,7 @@
         <v>41578</v>
       </c>
       <c r="B78" t="n">
-        <v>13.81081581115723</v>
+        <v>13.81081867218018</v>
       </c>
       <c r="C78" t="n">
         <v>25.78998947143555</v>
@@ -2261,7 +2261,7 @@
         <v>41608</v>
       </c>
       <c r="B79" t="n">
-        <v>15.01951885223389</v>
+        <v>15.01953029632568</v>
       </c>
       <c r="C79" t="n">
         <v>28.04710578918457</v>
@@ -2290,7 +2290,7 @@
         <v>41639</v>
       </c>
       <c r="B80" t="n">
-        <v>16.55406379699707</v>
+        <v>16.55405616760254</v>
       </c>
       <c r="C80" t="n">
         <v>30.91265869140625</v>
@@ -2319,7 +2319,7 @@
         <v>41670</v>
       </c>
       <c r="B81" t="n">
-        <v>17.21096611022949</v>
+        <v>17.21096420288086</v>
       </c>
       <c r="C81" t="n">
         <v>32.13935089111328</v>
@@ -2348,7 +2348,7 @@
         <v>41698</v>
       </c>
       <c r="B82" t="n">
-        <v>17.85240364074707</v>
+        <v>17.8524055480957</v>
       </c>
       <c r="C82" t="n">
         <v>32.72816467285156</v>
@@ -2377,7 +2377,7 @@
         <v>41729</v>
       </c>
       <c r="B83" t="n">
-        <v>17.79887771606445</v>
+        <v>17.79887199401855</v>
       </c>
       <c r="C83" t="n">
         <v>32.63002777099609</v>
@@ -2406,7 +2406,7 @@
         <v>41759</v>
       </c>
       <c r="B84" t="n">
-        <v>15.97957515716553</v>
+        <v>15.97957229614258</v>
       </c>
       <c r="C84" t="n">
         <v>28.97939109802246</v>
@@ -2435,7 +2435,7 @@
         <v>41790</v>
       </c>
       <c r="B85" t="n">
-        <v>16.81832695007324</v>
+        <v>16.81833457946777</v>
       </c>
       <c r="C85" t="n">
         <v>30.50049018859863</v>
@@ -2464,7 +2464,7 @@
         <v>41820</v>
       </c>
       <c r="B86" t="n">
-        <v>18.09539794921875</v>
+        <v>18.09539604187012</v>
       </c>
       <c r="C86" t="n">
         <v>32.81648635864258</v>
@@ -2493,7 +2493,7 @@
         <v>41851</v>
       </c>
       <c r="B87" t="n">
-        <v>17.95834922790527</v>
+        <v>17.95834732055664</v>
       </c>
       <c r="C87" t="n">
         <v>32.07065963745117</v>
@@ -2551,7 +2551,7 @@
         <v>41912</v>
       </c>
       <c r="B89" t="n">
-        <v>17.29892539978027</v>
+        <v>17.29891967773438</v>
       </c>
       <c r="C89" t="n">
         <v>30.89303207397461</v>
@@ -2580,7 +2580,7 @@
         <v>41943</v>
       </c>
       <c r="B90" t="n">
-        <v>16.79129600524902</v>
+        <v>16.79129791259766</v>
       </c>
       <c r="C90" t="n">
         <v>29.55839157104492</v>
@@ -2609,7 +2609,7 @@
         <v>41973</v>
       </c>
       <c r="B91" t="n">
-        <v>18.68672943115234</v>
+        <v>18.68672561645508</v>
       </c>
       <c r="C91" t="n">
         <v>32.89499664306641</v>
@@ -2638,7 +2638,7 @@
         <v>42004</v>
       </c>
       <c r="B92" t="n">
-        <v>18.85954284667969</v>
+        <v>18.85954475402832</v>
       </c>
       <c r="C92" t="n">
         <v>33.19921493530273</v>
@@ -2667,7 +2667,7 @@
         <v>42035</v>
       </c>
       <c r="B93" t="n">
-        <v>20.8163013458252</v>
+        <v>20.81630325317383</v>
       </c>
       <c r="C93" t="n">
         <v>36.64376831054688</v>
@@ -2696,7 +2696,7 @@
         <v>42063</v>
       </c>
       <c r="B94" t="n">
-        <v>21.33044624328613</v>
+        <v>21.3304443359375</v>
       </c>
       <c r="C94" t="n">
         <v>36.76153182983398</v>
@@ -2725,7 +2725,7 @@
         <v>42094</v>
       </c>
       <c r="B95" t="n">
-        <v>22.14472007751465</v>
+        <v>22.14471817016602</v>
       </c>
       <c r="C95" t="n">
         <v>38.16486740112305</v>
@@ -2754,7 +2754,7 @@
         <v>42124</v>
       </c>
       <c r="B96" t="n">
-        <v>23.83131980895996</v>
+        <v>23.83131408691406</v>
       </c>
       <c r="C96" t="n">
         <v>40.19626998901367</v>
@@ -2783,7 +2783,7 @@
         <v>42155</v>
       </c>
       <c r="B97" t="n">
-        <v>25.48368835449219</v>
+        <v>25.48368453979492</v>
       </c>
       <c r="C97" t="n">
         <v>42.98331832885742</v>
@@ -2812,7 +2812,7 @@
         <v>42185</v>
       </c>
       <c r="B98" t="n">
-        <v>23.77895164489746</v>
+        <v>23.77895355224609</v>
       </c>
       <c r="C98" t="n">
         <v>40.10794830322266</v>
@@ -2841,7 +2841,7 @@
         <v>42216</v>
       </c>
       <c r="B99" t="n">
-        <v>23.25100326538086</v>
+        <v>23.25099945068359</v>
       </c>
       <c r="C99" t="n">
         <v>38.51815414428711</v>
@@ -2870,7 +2870,7 @@
         <v>42247</v>
       </c>
       <c r="B100" t="n">
-        <v>20.28908538818359</v>
+        <v>20.28908920288086</v>
       </c>
       <c r="C100" t="n">
         <v>33.61138534545898</v>
@@ -2899,7 +2899,7 @@
         <v>42277</v>
       </c>
       <c r="B101" t="n">
-        <v>18.7607421875</v>
+        <v>18.76073455810547</v>
       </c>
       <c r="C101" t="n">
         <v>31.07949066162109</v>
@@ -2957,7 +2957,7 @@
         <v>42338</v>
       </c>
       <c r="B103" t="n">
-        <v>19.13041496276855</v>
+        <v>19.13041305541992</v>
       </c>
       <c r="C103" t="n">
         <v>31.22999954223633</v>
@@ -2986,7 +2986,7 @@
         <v>42369</v>
       </c>
       <c r="B104" t="n">
-        <v>17.91141128540039</v>
+        <v>17.91140747070312</v>
       </c>
       <c r="C104" t="n">
         <v>29.23999977111816</v>
@@ -3044,7 +3044,7 @@
         <v>42429</v>
       </c>
       <c r="B106" t="n">
-        <v>16.28357124328613</v>
+        <v>16.28357315063477</v>
       </c>
       <c r="C106" t="n">
         <v>25.96999931335449</v>
@@ -3073,7 +3073,7 @@
         <v>42460</v>
       </c>
       <c r="B107" t="n">
-        <v>17.58776473999023</v>
+        <v>17.58776664733887</v>
       </c>
       <c r="C107" t="n">
         <v>28.04999923706055</v>
@@ -3102,7 +3102,7 @@
         <v>42490</v>
       </c>
       <c r="B108" t="n">
-        <v>17.37396621704102</v>
+        <v>17.37395858764648</v>
       </c>
       <c r="C108" t="n">
         <v>27.44000053405762</v>
@@ -3131,7 +3131,7 @@
         <v>42521</v>
       </c>
       <c r="B109" t="n">
-        <v>16.58251190185547</v>
+        <v>16.58251762390137</v>
       </c>
       <c r="C109" t="n">
         <v>26.19000053405762</v>
@@ -3160,7 +3160,7 @@
         <v>42551</v>
       </c>
       <c r="B110" t="n">
-        <v>15.53779220581055</v>
+        <v>15.53779697418213</v>
       </c>
       <c r="C110" t="n">
         <v>24.54000091552734</v>
@@ -3189,7 +3189,7 @@
         <v>42582</v>
       </c>
       <c r="B111" t="n">
-        <v>17.21949005126953</v>
+        <v>17.21948623657227</v>
       </c>
       <c r="C111" t="n">
         <v>26.84000015258789</v>
@@ -3247,7 +3247,7 @@
         <v>42643</v>
       </c>
       <c r="B113" t="n">
-        <v>16.37904167175293</v>
+        <v>16.37904357910156</v>
       </c>
       <c r="C113" t="n">
         <v>25.53000068664551</v>
@@ -3276,7 +3276,7 @@
         <v>42674</v>
       </c>
       <c r="B114" t="n">
-        <v>16.05826377868652</v>
+        <v>16.05826759338379</v>
       </c>
       <c r="C114" t="n">
         <v>25.03000068664551</v>
@@ -3305,7 +3305,7 @@
         <v>42704</v>
       </c>
       <c r="B115" t="n">
-        <v>16.79647064208984</v>
+        <v>16.79647254943848</v>
       </c>
       <c r="C115" t="n">
         <v>25.73999977111816</v>
@@ -3334,7 +3334,7 @@
         <v>42735</v>
       </c>
       <c r="B116" t="n">
-        <v>17.63825607299805</v>
+        <v>17.63825225830078</v>
       </c>
       <c r="C116" t="n">
         <v>27.03000068664551</v>
@@ -3363,7 +3363,7 @@
         <v>42766</v>
       </c>
       <c r="B117" t="n">
-        <v>19.9874095916748</v>
+        <v>19.98740768432617</v>
       </c>
       <c r="C117" t="n">
         <v>30.6299991607666</v>
@@ -3392,7 +3392,7 @@
         <v>42794</v>
       </c>
       <c r="B118" t="n">
-        <v>19.57133674621582</v>
+        <v>19.57134056091309</v>
       </c>
       <c r="C118" t="n">
         <v>29.54000091552734</v>
@@ -3421,7 +3421,7 @@
         <v>42825</v>
       </c>
       <c r="B119" t="n">
-        <v>19.67734718322754</v>
+        <v>19.67734336853027</v>
       </c>
       <c r="C119" t="n">
         <v>29.70000076293945</v>
@@ -3450,7 +3450,7 @@
         <v>42855</v>
       </c>
       <c r="B120" t="n">
-        <v>21.01738739013672</v>
+        <v>21.01738357543945</v>
       </c>
       <c r="C120" t="n">
         <v>30.84000015258789</v>
@@ -3479,7 +3479,7 @@
         <v>42886</v>
       </c>
       <c r="B121" t="n">
-        <v>22.40764236450195</v>
+        <v>22.40763854980469</v>
       </c>
       <c r="C121" t="n">
         <v>32.88000106811523</v>
@@ -3537,7 +3537,7 @@
         <v>42947</v>
       </c>
       <c r="B123" t="n">
-        <v>23.1586799621582</v>
+        <v>23.1586856842041</v>
       </c>
       <c r="C123" t="n">
         <v>33.45000076293945</v>
@@ -3595,7 +3595,7 @@
         <v>43008</v>
       </c>
       <c r="B125" t="n">
-        <v>23.10330009460449</v>
+        <v>23.10329818725586</v>
       </c>
       <c r="C125" t="n">
         <v>33.36999893188477</v>
@@ -3653,7 +3653,7 @@
         <v>43069</v>
       </c>
       <c r="B127" t="n">
-        <v>22.25085639953613</v>
+        <v>22.25085830688477</v>
       </c>
       <c r="C127" t="n">
         <v>31.71999931335449</v>
@@ -3682,7 +3682,7 @@
         <v>43100</v>
       </c>
       <c r="B128" t="n">
-        <v>22.46129417419434</v>
+        <v>22.4612979888916</v>
       </c>
       <c r="C128" t="n">
         <v>32.02000045776367</v>
@@ -3711,7 +3711,7 @@
         <v>43131</v>
       </c>
       <c r="B129" t="n">
-        <v>25.63898849487305</v>
+        <v>25.63899230957031</v>
       </c>
       <c r="C129" t="n">
         <v>36.54999923706055</v>
@@ -3740,7 +3740,7 @@
         <v>43159</v>
       </c>
       <c r="B130" t="n">
-        <v>24.46361351013184</v>
+        <v>24.46361923217773</v>
       </c>
       <c r="C130" t="n">
         <v>34</v>
@@ -3769,7 +3769,7 @@
         <v>43190</v>
       </c>
       <c r="B131" t="n">
-        <v>22.98861503601074</v>
+        <v>22.98861122131348</v>
       </c>
       <c r="C131" t="n">
         <v>31.95000076293945</v>
@@ -3798,7 +3798,7 @@
         <v>43220</v>
       </c>
       <c r="B132" t="n">
-        <v>22.51922416687012</v>
+        <v>22.51922225952148</v>
       </c>
       <c r="C132" t="n">
         <v>30.95000076293945</v>
@@ -3827,7 +3827,7 @@
         <v>43251</v>
       </c>
       <c r="B133" t="n">
-        <v>23.23226737976074</v>
+        <v>23.23227310180664</v>
       </c>
       <c r="C133" t="n">
         <v>31.93000030517578</v>
@@ -3885,7 +3885,7 @@
         <v>43312</v>
       </c>
       <c r="B135" t="n">
-        <v>25.82384300231934</v>
+        <v>25.8238410949707</v>
       </c>
       <c r="C135" t="n">
         <v>34.91999816894531</v>
@@ -3914,7 +3914,7 @@
         <v>43343</v>
       </c>
       <c r="B136" t="n">
-        <v>27.29547691345215</v>
+        <v>27.29548835754395</v>
       </c>
       <c r="C136" t="n">
         <v>36.90999984741211</v>
@@ -3943,7 +3943,7 @@
         <v>43373</v>
       </c>
       <c r="B137" t="n">
-        <v>28.16070747375488</v>
+        <v>28.16071128845215</v>
       </c>
       <c r="C137" t="n">
         <v>38.08000183105469</v>
@@ -3972,7 +3972,7 @@
         <v>43404</v>
       </c>
       <c r="B138" t="n">
-        <v>24.40780830383301</v>
+        <v>24.40781021118164</v>
       </c>
       <c r="C138" t="n">
         <v>32.36000061035156</v>
@@ -4059,7 +4059,7 @@
         <v>43496</v>
       </c>
       <c r="B141" t="n">
-        <v>25.41851615905762</v>
+        <v>25.41852188110352</v>
       </c>
       <c r="C141" t="n">
         <v>33.70000076293945</v>
@@ -4088,7 +4088,7 @@
         <v>43524</v>
       </c>
       <c r="B142" t="n">
-        <v>25.61520385742188</v>
+        <v>25.61520576477051</v>
       </c>
       <c r="C142" t="n">
         <v>33.38999938964844</v>
@@ -4146,7 +4146,7 @@
         <v>43585</v>
       </c>
       <c r="B144" t="n">
-        <v>30.55345153808594</v>
+        <v>30.5534496307373</v>
       </c>
       <c r="C144" t="n">
         <v>39.45999908447266</v>
@@ -4204,7 +4204,7 @@
         <v>43646</v>
       </c>
       <c r="B146" t="n">
-        <v>34.39391326904297</v>
+        <v>34.39392471313477</v>
       </c>
       <c r="C146" t="n">
         <v>44.41999816894531</v>
@@ -4233,7 +4233,7 @@
         <v>43677</v>
       </c>
       <c r="B147" t="n">
-        <v>37.51254272460938</v>
+        <v>37.51254653930664</v>
       </c>
       <c r="C147" t="n">
         <v>47.97999954223633</v>
@@ -4262,7 +4262,7 @@
         <v>43708</v>
       </c>
       <c r="B148" t="n">
-        <v>38.90421295166016</v>
+        <v>38.90420913696289</v>
       </c>
       <c r="C148" t="n">
         <v>49.7599983215332</v>
@@ -4291,7 +4291,7 @@
         <v>43738</v>
       </c>
       <c r="B149" t="n">
-        <v>38.1849250793457</v>
+        <v>38.18492126464844</v>
       </c>
       <c r="C149" t="n">
         <v>48.84000015258789</v>
@@ -4320,7 +4320,7 @@
         <v>43769</v>
       </c>
       <c r="B150" t="n">
-        <v>41.56246185302734</v>
+        <v>41.56245803833008</v>
       </c>
       <c r="C150" t="n">
         <v>53.15999984741211</v>
@@ -4349,7 +4349,7 @@
         <v>43799</v>
       </c>
       <c r="B151" t="n">
-        <v>42.78557968139648</v>
+        <v>42.78558349609375</v>
       </c>
       <c r="C151" t="n">
         <v>54.22000122070312</v>
@@ -4378,7 +4378,7 @@
         <v>43830</v>
       </c>
       <c r="B152" t="n">
-        <v>44.14284515380859</v>
+        <v>44.14284133911133</v>
       </c>
       <c r="C152" t="n">
         <v>55.93999862670898</v>
@@ -4407,7 +4407,7 @@
         <v>43861</v>
       </c>
       <c r="B153" t="n">
-        <v>48.19099044799805</v>
+        <v>48.19097900390625</v>
       </c>
       <c r="C153" t="n">
         <v>61.06999969482422</v>
@@ -4436,7 +4436,7 @@
         <v>43890</v>
       </c>
       <c r="B154" t="n">
-        <v>42.8931999206543</v>
+        <v>42.89320755004883</v>
       </c>
       <c r="C154" t="n">
         <v>53.84000015258789</v>
@@ -4465,7 +4465,7 @@
         <v>43921</v>
       </c>
       <c r="B155" t="n">
-        <v>36.30466079711914</v>
+        <v>36.30467224121094</v>
       </c>
       <c r="C155" t="n">
         <v>45.56999969482422</v>
@@ -4494,7 +4494,7 @@
         <v>43951</v>
       </c>
       <c r="B156" t="n">
-        <v>41.61852645874023</v>
+        <v>41.61852264404297</v>
       </c>
       <c r="C156" t="n">
         <v>52.2400016784668</v>
@@ -4523,7 +4523,7 @@
         <v>43982</v>
       </c>
       <c r="B157" t="n">
-        <v>45.59173583984375</v>
+        <v>45.59173965454102</v>
       </c>
       <c r="C157" t="n">
         <v>56.79999923706055</v>
@@ -4552,7 +4552,7 @@
         <v>44012</v>
       </c>
       <c r="B158" t="n">
-        <v>45.47937774658203</v>
+        <v>45.4793815612793</v>
       </c>
       <c r="C158" t="n">
         <v>56.65999984741211</v>
@@ -4581,7 +4581,7 @@
         <v>44043</v>
       </c>
       <c r="B159" t="n">
-        <v>43.05774307250977</v>
+        <v>43.0577392578125</v>
       </c>
       <c r="C159" t="n">
         <v>53.27999877929688</v>
@@ -4610,7 +4610,7 @@
         <v>44074</v>
       </c>
       <c r="B160" t="n">
-        <v>42.79106140136719</v>
+        <v>42.79107284545898</v>
       </c>
       <c r="C160" t="n">
         <v>52.95000076293945</v>
@@ -4639,7 +4639,7 @@
         <v>44104</v>
       </c>
       <c r="B161" t="n">
-        <v>42.18495178222656</v>
+        <v>42.18495559692383</v>
       </c>
       <c r="C161" t="n">
         <v>52.20000076293945</v>
@@ -4668,7 +4668,7 @@
         <v>44135</v>
       </c>
       <c r="B162" t="n">
-        <v>40.74646377563477</v>
+        <v>40.74646759033203</v>
       </c>
       <c r="C162" t="n">
         <v>50.41999816894531</v>
@@ -4697,7 +4697,7 @@
         <v>44165</v>
       </c>
       <c r="B163" t="n">
-        <v>48.58142471313477</v>
+        <v>48.58142852783203</v>
       </c>
       <c r="C163" t="n">
         <v>59.54999923706055</v>
@@ -4726,7 +4726,7 @@
         <v>44196</v>
       </c>
       <c r="B164" t="n">
-        <v>52.87258529663086</v>
+        <v>52.87257766723633</v>
       </c>
       <c r="C164" t="n">
         <v>64.80999755859375</v>
@@ -4755,7 +4755,7 @@
         <v>44227</v>
       </c>
       <c r="B165" t="n">
-        <v>54.8142204284668</v>
+        <v>54.814208984375</v>
       </c>
       <c r="C165" t="n">
         <v>67.19000244140625</v>
@@ -4784,7 +4784,7 @@
         <v>44255</v>
       </c>
       <c r="B166" t="n">
-        <v>57.2526969909668</v>
+        <v>57.25270462036133</v>
       </c>
       <c r="C166" t="n">
         <v>69.23000335693359</v>
@@ -4813,7 +4813,7 @@
         <v>44286</v>
       </c>
       <c r="B167" t="n">
-        <v>61.6357536315918</v>
+        <v>61.63574981689453</v>
       </c>
       <c r="C167" t="n">
         <v>74.52999877929688</v>
@@ -4871,7 +4871,7 @@
         <v>44347</v>
       </c>
       <c r="B169" t="n">
-        <v>77.34603118896484</v>
+        <v>77.34603881835938</v>
       </c>
       <c r="C169" t="n">
         <v>92.66999816894531</v>
@@ -4987,7 +4987,7 @@
         <v>44469</v>
       </c>
       <c r="B173" t="n">
-        <v>97.68792724609375</v>
+        <v>97.68791961669922</v>
       </c>
       <c r="C173" t="n">
         <v>116.3399963378906</v>
@@ -5016,7 +5016,7 @@
         <v>44500</v>
       </c>
       <c r="B174" t="n">
-        <v>117.1441650390625</v>
+        <v>117.1441421508789</v>
       </c>
       <c r="C174" t="n">
         <v>138.4199981689453</v>
@@ -5045,7 +5045,7 @@
         <v>44530</v>
       </c>
       <c r="B175" t="n">
-        <v>119.7084350585938</v>
+        <v>119.7084274291992</v>
       </c>
       <c r="C175" t="n">
         <v>141.4499969482422</v>
@@ -5074,7 +5074,7 @@
         <v>44561</v>
       </c>
       <c r="B176" t="n">
-        <v>109.5021209716797</v>
+        <v>109.5021133422852</v>
       </c>
       <c r="C176" t="n">
         <v>129.3899993896484</v>
@@ -5161,7 +5161,7 @@
         <v>44651</v>
       </c>
       <c r="B179" t="n">
-        <v>108.6030731201172</v>
+        <v>108.6030883789062</v>
       </c>
       <c r="C179" t="n">
         <v>126.9400024414062</v>
@@ -5190,7 +5190,7 @@
         <v>44681</v>
       </c>
       <c r="B180" t="n">
-        <v>87.97017669677734</v>
+        <v>87.97018432617188</v>
       </c>
       <c r="C180" t="n">
         <v>101.5699996948242</v>
@@ -5277,7 +5277,7 @@
         <v>44773</v>
       </c>
       <c r="B183" t="n">
-        <v>89.51253509521484</v>
+        <v>89.51252746582031</v>
       </c>
       <c r="C183" t="n">
         <v>102.0699996948242</v>
@@ -5335,7 +5335,7 @@
         <v>44834</v>
       </c>
       <c r="B185" t="n">
-        <v>73.40254211425781</v>
+        <v>73.40255737304688</v>
       </c>
       <c r="C185" t="n">
         <v>83.69999694824219</v>
@@ -5364,7 +5364,7 @@
         <v>44865</v>
       </c>
       <c r="B186" t="n">
-        <v>80.70446014404297</v>
+        <v>80.70447540283203</v>
       </c>
       <c r="C186" t="n">
         <v>91.13999938964844</v>
@@ -5393,7 +5393,7 @@
         <v>44895</v>
       </c>
       <c r="B187" t="n">
-        <v>81.0498046875</v>
+        <v>81.04979705810547</v>
       </c>
       <c r="C187" t="n">
         <v>91.52999877929688</v>
@@ -5422,7 +5422,7 @@
         <v>44926</v>
       </c>
       <c r="B188" t="n">
-        <v>65.69525146484375</v>
+        <v>65.69524383544922</v>
       </c>
       <c r="C188" t="n">
         <v>74.19000244140625</v>
@@ -5451,7 +5451,7 @@
         <v>44957</v>
       </c>
       <c r="B189" t="n">
-        <v>84.97257995605469</v>
+        <v>84.97256469726562</v>
       </c>
       <c r="C189" t="n">
         <v>95.95999908447266</v>
@@ -5480,7 +5480,7 @@
         <v>44985</v>
       </c>
       <c r="B190" t="n">
-        <v>81.14157104492188</v>
+        <v>81.14156341552734</v>
       </c>
       <c r="C190" t="n">
         <v>90.80000305175781</v>
@@ -5509,7 +5509,7 @@
         <v>45016</v>
       </c>
       <c r="B191" t="n">
-        <v>78.49642944335938</v>
+        <v>78.49643707275391</v>
       </c>
       <c r="C191" t="n">
         <v>87.83999633789062</v>
@@ -5538,7 +5538,7 @@
         <v>45046</v>
       </c>
       <c r="B192" t="n">
-        <v>80.58625030517578</v>
+        <v>80.58625793457031</v>
       </c>
       <c r="C192" t="n">
         <v>89.33000183105469</v>
@@ -5567,7 +5567,7 @@
         <v>45077</v>
       </c>
       <c r="B193" t="n">
-        <v>77.25743865966797</v>
+        <v>77.2574462890625</v>
       </c>
       <c r="C193" t="n">
         <v>85.63999938964844</v>
@@ -5596,7 +5596,7 @@
         <v>45107</v>
       </c>
       <c r="B194" t="n">
-        <v>83.86997985839844</v>
+        <v>83.86997222900391</v>
       </c>
       <c r="C194" t="n">
         <v>92.97000122070312</v>
@@ -5654,7 +5654,7 @@
         <v>45169</v>
       </c>
       <c r="B196" t="n">
-        <v>96.69802093505859</v>
+        <v>96.69801330566406</v>
       </c>
       <c r="C196" t="n">
         <v>106.370002746582</v>
@@ -5683,7 +5683,7 @@
         <v>45199</v>
       </c>
       <c r="B197" t="n">
-        <v>97.39800262451172</v>
+        <v>97.39799499511719</v>
       </c>
       <c r="C197" t="n">
         <v>107.1399993896484</v>
@@ -5712,7 +5712,7 @@
         <v>45230</v>
       </c>
       <c r="B198" t="n">
-        <v>84.68683624267578</v>
+        <v>84.68682861328125</v>
       </c>
       <c r="C198" t="n">
         <v>92.34999847412109</v>
@@ -5741,7 +5741,7 @@
         <v>45260</v>
       </c>
       <c r="B199" t="n">
-        <v>103.0455932617188</v>
+        <v>103.0456008911133</v>
       </c>
       <c r="C199" t="n">
         <v>112.370002746582</v>
@@ -5770,7 +5770,7 @@
         <v>45291</v>
       </c>
       <c r="B200" t="n">
-        <v>120.0563049316406</v>
+        <v>120.0563354492188</v>
       </c>
       <c r="C200" t="n">
         <v>130.9199981689453</v>
@@ -5799,7 +5799,7 @@
         <v>45322</v>
       </c>
       <c r="B201" t="n">
-        <v>114.1231994628906</v>
+        <v>114.1231842041016</v>
       </c>
       <c r="C201" t="n">
         <v>124.4499969482422</v>
@@ -5828,7 +5828,7 @@
         <v>45351</v>
       </c>
       <c r="B202" t="n">
-        <v>118.1067123413086</v>
+        <v>118.1067199707031</v>
       </c>
       <c r="C202" t="n">
         <v>127.8199996948242</v>
@@ -5857,7 +5857,7 @@
         <v>45382</v>
       </c>
       <c r="B203" t="n">
-        <v>121.3869400024414</v>
+        <v>121.3869323730469</v>
       </c>
       <c r="C203" t="n">
         <v>131.3699951171875</v>
@@ -5886,7 +5886,7 @@
         <v>45412</v>
       </c>
       <c r="B204" t="n">
-        <v>108.4784545898438</v>
+        <v>108.4784622192383</v>
       </c>
       <c r="C204" t="n">
         <v>116.6100006103516</v>
@@ -5944,7 +5944,7 @@
         <v>45473</v>
       </c>
       <c r="B206" t="n">
-        <v>115.1670837402344</v>
+        <v>115.1670761108398</v>
       </c>
       <c r="C206" t="n">
         <v>123.8000030517578</v>
@@ -5973,7 +5973,7 @@
         <v>45504</v>
       </c>
       <c r="B207" t="n">
-        <v>133.0055541992188</v>
+        <v>133.0055389404297</v>
       </c>
       <c r="C207" t="n">
         <v>142.1499938964844</v>
@@ -6031,7 +6031,7 @@
         <v>45565</v>
       </c>
       <c r="B209" t="n">
-        <v>143.2792053222656</v>
+        <v>143.2792205810547</v>
       </c>
       <c r="C209" t="n">
         <v>153.1300048828125</v>
@@ -6060,7 +6060,7 @@
         <v>45596</v>
       </c>
       <c r="B210" t="n">
-        <v>157.7687377929688</v>
+        <v>157.7687530517578</v>
       </c>
       <c r="C210" t="n">
         <v>167.75</v>
@@ -6089,7 +6089,7 @@
         <v>45626</v>
       </c>
       <c r="B211" t="n">
-        <v>179.7199859619141</v>
+        <v>179.7200012207031</v>
       </c>
       <c r="C211" t="n">
         <v>191.0899963378906</v>
@@ -6118,7 +6118,7 @@
         <v>45657</v>
       </c>
       <c r="B212" t="n">
-        <v>162.160888671875</v>
+        <v>162.1609039306641</v>
       </c>
       <c r="C212" t="n">
         <v>172.4199981689453</v>
@@ -6147,7 +6147,7 @@
         <v>45688</v>
       </c>
       <c r="B213" t="n">
-        <v>166.5718078613281</v>
+        <v>166.5718231201172</v>
       </c>
       <c r="C213" t="n">
         <v>177.1100006103516</v>
@@ -6176,7 +6176,7 @@
         <v>45716</v>
       </c>
       <c r="B214" t="n">
-        <v>152.8636627197266</v>
+        <v>152.8636474609375</v>
       </c>
       <c r="C214" t="n">
         <v>161.1600036621094</v>
@@ -6205,7 +6205,7 @@
         <v>45747</v>
       </c>
       <c r="B215" t="n">
-        <v>132.5842742919922</v>
+        <v>132.5842895507812</v>
       </c>
       <c r="C215" t="n">
         <v>139.7799987792969</v>
@@ -6234,7 +6234,7 @@
         <v>45777</v>
       </c>
       <c r="B216" t="n">
-        <v>125.8103561401367</v>
+        <v>125.8103713989258</v>
       </c>
       <c r="C216" t="n">
         <v>131.7100067138672</v>
@@ -6263,7 +6263,7 @@
         <v>45808</v>
       </c>
       <c r="B217" t="n">
-        <v>132.5445556640625</v>
+        <v>132.5445709228516</v>
       </c>
       <c r="C217" t="n">
         <v>138.7599945068359</v>
@@ -6292,7 +6292,7 @@
         <v>45838</v>
       </c>
       <c r="B218" t="n">
-        <v>142.8799133300781</v>
+        <v>142.8799285888672</v>
       </c>
       <c r="C218" t="n">
         <v>149.5800018310547</v>
@@ -6321,7 +6321,7 @@
         <v>45869</v>
       </c>
       <c r="B219" t="n">
-        <v>165.2126770019531</v>
+        <v>165.2126922607422</v>
       </c>
       <c r="C219" t="n">
         <v>172.9600067138672</v>
